--- a/Excel/Data/2023/국내 여행로그 데이터_수도권_2023_merge/통합/국내여행로그데이터_수도권_컬럼설명통합문서_20260730.xlsx
+++ b/Excel/Data/2023/국내 여행로그 데이터_수도권_2023_merge/통합/국내여행로그데이터_수도권_컬럼설명통합문서_20260730.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\Mika\004 학습\008 잇다고\프로젝트\프로젝트 파일\국내 여행로그 데이터_수도권_2023_merge\통합\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\파워BI레인저\Python\Excel\Data\2023\국내 여행로그 데이터_수도권_2023_merge\통합\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CC2B857-DF8B-44DC-869D-62BAB35ACEBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{195F25DA-C429-4AD2-93FF-DAF7B3164376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{A2DB9FAD-6DF8-4397-A116-F9E2EFF01B57}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="3" xr2:uid="{A2DB9FAD-6DF8-4397-A116-F9E2EFF01B57}"/>
   </bookViews>
   <sheets>
     <sheet name="tc_codea (코드 A)" sheetId="16" r:id="rId1"/>
@@ -618,599 +618,991 @@
     <t>TRAVEL_MISSION_CHECK</t>
   </si>
   <si>
-    <t>여행 중 수행 미션 코드 (코드북 cd_a='MIS'). 예: 1=쇼핑, 5=야외스포츠, 9=지역축제 참가 등</t>
+    <t>여행 페르소나(텍스트/코드, 결측률 높음)</t>
+  </si>
+  <si>
+    <t>TRAVEL_PERSONA</t>
+  </si>
+  <si>
+    <t>주 이용 이동수단명(텍스트)</t>
+  </si>
+  <si>
+    <t>MVMN_NM</t>
+  </si>
+  <si>
+    <t>여행 종료일</t>
+  </si>
+  <si>
+    <t>TRAVEL_END_YMD</t>
+  </si>
+  <si>
+    <t>여행 시작일</t>
+  </si>
+  <si>
+    <t>TRAVEL_START_YMD</t>
+  </si>
+  <si>
+    <t>여행자 식별자. tn_traveller_master.TRAVELER_ID와 조인</t>
+  </si>
+  <si>
+    <t>TRAVELER_ID</t>
+  </si>
+  <si>
+    <t>여행명(자유 텍스트)</t>
+  </si>
+  <si>
+    <t>TRAVEL_NM</t>
+  </si>
+  <si>
+    <t>여행 고유 식별자. 다른 모든 여행 단위 테이블의 조인 키</t>
+  </si>
+  <si>
+    <t>tn_travel (여행) — 여행 단위 마스터 — 컬럼 설명</t>
+  </si>
+  <si>
+    <t>본인을 제외한 동반자 수(응답자 기재값)</t>
+  </si>
+  <si>
+    <t>TRAVEL_COMPANIONS_NUM</t>
+  </si>
+  <si>
+    <t>여행 동기 코드 3순위 (코드북 cd_a='TMT')</t>
+  </si>
+  <si>
+    <t>TRAVEL_MOTIVE_3</t>
+  </si>
+  <si>
+    <t>여행 동기 코드 2순위 (코드북 cd_a='TMT')</t>
+  </si>
+  <si>
+    <t>TRAVEL_MOTIVE_2</t>
+  </si>
+  <si>
+    <t>여행 동기 코드 1순위 (코드북 cd_a='TMT')</t>
+  </si>
+  <si>
+    <t>TRAVEL_MOTIVE_1</t>
+  </si>
+  <si>
+    <t>여행 기간(시작~종료일 텍스트)</t>
+  </si>
+  <si>
+    <t>TRAVEL_STATUS_YMD</t>
+  </si>
+  <si>
+    <t>동반유형 요약(텍스트). 예: 나홀로 여행, 2인 가족 여행, 자녀 동반 여행 등 — tn_companion_info의 실제 동반자 수와 불일치 사례가 있음을 EDA에서 확인</t>
+  </si>
+  <si>
+    <t>TRAVEL_STATUS_ACCOMPANY</t>
+  </si>
+  <si>
+    <t>여행 목적지(시/도 단위 텍스트)</t>
+  </si>
+  <si>
+    <t>TRAVEL_STATUS_DESTINATION</t>
+  </si>
+  <si>
+    <t>여행 당시 거주지(시/도 단위 텍스트)</t>
+  </si>
+  <si>
+    <t>TRAVEL_STATUS_RESIDENCE</t>
+  </si>
+  <si>
+    <t>여행스타일 축8 (1~7 척도)</t>
+  </si>
+  <si>
+    <t>TRAVEL_STYL_8</t>
+  </si>
+  <si>
+    <t>여행스타일 축7 (1~7 척도)</t>
+  </si>
+  <si>
+    <t>TRAVEL_STYL_7</t>
+  </si>
+  <si>
+    <t>여행스타일 축6 (1~7 척도)</t>
+  </si>
+  <si>
+    <t>TRAVEL_STYL_6</t>
+  </si>
+  <si>
+    <t>여행스타일 축5 (1~7 척도)</t>
+  </si>
+  <si>
+    <t>TRAVEL_STYL_5</t>
+  </si>
+  <si>
+    <t>여행스타일 축4 (1~7 척도)</t>
+  </si>
+  <si>
+    <t>TRAVEL_STYL_4</t>
+  </si>
+  <si>
+    <t>여행스타일 축3 (1~7 척도)</t>
+  </si>
+  <si>
+    <t>TRAVEL_STYL_3</t>
+  </si>
+  <si>
+    <t>여행스타일 축2 (1~7 척도, 축 주제는 설문 문항 원문 확인 필요)</t>
+  </si>
+  <si>
+    <t>TRAVEL_STYL_2</t>
+  </si>
+  <si>
+    <t>여행스타일 축1: 자연(1) ↔ 도시(7) 선호도 (코드북 cd_a='TSY', 1~7 척도)</t>
+  </si>
+  <si>
+    <t>TRAVEL_STYL_1</t>
+  </si>
+  <si>
+    <t>선호 여행지 시군구 코드 3순위</t>
+  </si>
+  <si>
+    <t>TRAVEL_LIKE_SGG_3</t>
+  </si>
+  <si>
+    <t>선호 여행지 시/도 코드 3순위</t>
+  </si>
+  <si>
+    <t>TRAVEL_LIKE_SIDO_3</t>
+  </si>
+  <si>
+    <t>선호 여행지 시군구 코드 2순위</t>
+  </si>
+  <si>
+    <t>TRAVEL_LIKE_SGG_2</t>
+  </si>
+  <si>
+    <t>선호 여행지 시/도 코드 2순위</t>
+  </si>
+  <si>
+    <t>TRAVEL_LIKE_SIDO_2</t>
+  </si>
+  <si>
+    <t>선호 여행지 시군구 코드 1순위</t>
+  </si>
+  <si>
+    <t>TRAVEL_LIKE_SGG_1</t>
+  </si>
+  <si>
+    <t>선호 여행지 시/도 코드 1순위 (코드북 cd_a='TAR')</t>
+  </si>
+  <si>
+    <t>TRAVEL_LIKE_SIDO_1</t>
+  </si>
+  <si>
+    <t>최근 기간 내 여행 횟수</t>
+  </si>
+  <si>
+    <t>TRAVEL_NUM</t>
+  </si>
+  <si>
+    <t>여행 빈도_기간 코드 (코드북 cd_a='TTM'). 1=1주일, 2=한달, 3=1년 등</t>
+  </si>
+  <si>
+    <t>TRAVEL_TERM</t>
+  </si>
+  <si>
+    <t>가구소득 구간 코드 (코드북 cd_a='INC')</t>
+  </si>
+  <si>
+    <t>HOUSE_INCOME</t>
+  </si>
+  <si>
+    <t>개인소득 구간 코드 (코드북 cd_a='INC', 1~12 구간)</t>
+  </si>
+  <si>
+    <t>INCOME</t>
+  </si>
+  <si>
+    <t>직업이 '기타'일 때의 상세 텍스트(결측률 매우 높음, 95%대)</t>
+  </si>
+  <si>
+    <t>JOB_ETC</t>
+  </si>
+  <si>
+    <t>직업 코드 (코드북 cd_a='JOB')</t>
+  </si>
+  <si>
+    <t>JOB_NM</t>
+  </si>
+  <si>
+    <t>가족 구성원 수</t>
+  </si>
+  <si>
+    <t>FAMILY_MEMB</t>
+  </si>
+  <si>
+    <t>혼인상태 코드 (코드북 cd_a='MAR')</t>
+  </si>
+  <si>
+    <t>MARR_STTS</t>
+  </si>
+  <si>
+    <t>최종학력 이수 여부 코드 (코드북 cd_a='EFS')</t>
+  </si>
+  <si>
+    <t>EDU_FNSH_SE</t>
+  </si>
+  <si>
+    <t>최종학력 코드 (코드북 cd_a='EDU')</t>
+  </si>
+  <si>
+    <t>EDU_NM</t>
+  </si>
+  <si>
+    <t>연령대(10대 단위, 예: 20/30/40/50/60)</t>
+  </si>
+  <si>
+    <t>AGE_GRP</t>
+  </si>
+  <si>
+    <t>성별</t>
+  </si>
+  <si>
+    <t>GENDER</t>
+  </si>
+  <si>
+    <t>거주지 시군구 코드. tc_sgg와 조인</t>
+  </si>
+  <si>
+    <t>RESIDENCE_SGG_CD</t>
+  </si>
+  <si>
+    <t>여행객 고유 식별자. tn_travel.TRAVELER_ID와 조인</t>
+  </si>
+  <si>
+    <t>tn_traveller_master (여행객 Master) — 여행객 인구통계·성향 마스터 — 컬럼 설명</t>
+  </si>
+  <si>
+    <t>방문지의 시군구 코드. tc_sgg와 조인 (결측률 높음)</t>
+  </si>
+  <si>
+    <t>추천 의향 점수 (코드북 cd_a='REC', 1~5점)</t>
+  </si>
+  <si>
+    <t>RCMDTN_INTENTION</t>
+  </si>
+  <si>
+    <t>재방문 의향 점수 (코드북 cd_a='REP', 1~5점)</t>
+  </si>
+  <si>
+    <t>REVISIT_INTENTION</t>
+  </si>
+  <si>
+    <t>전반적 만족도 점수 (코드북 cd_a='DGS', 1~5점). 비관광지(21~24)는 결측률 74%</t>
+  </si>
+  <si>
+    <t>DGSTFN</t>
+  </si>
+  <si>
+    <t>숙소 유형 코드 (코드북 cd_a='HTY', 방문지 유형이 숙소인 경우만 값 존재)</t>
+  </si>
+  <si>
+    <t>방문 선택 이유 코드 (코드북 cd_a='REN'). 1=지명도/핫플레이스, 5=지인 추천 등</t>
+  </si>
+  <si>
+    <t>VISIT_CHC_REASON_CD</t>
+  </si>
+  <si>
+    <t>재방문 여부 코드 (코드북 cd_a='REV'). 1=처음 방문, 2=재방문</t>
+  </si>
+  <si>
+    <t>REVISIT_YN</t>
+  </si>
+  <si>
+    <t>방문지 유형 코드 (코드북 cd_a='VIS'). 1=자연관광지, 4=상업지구, 11=식당/카페, 21=집, 22=친구/친지집, 23=사무실, 24=숙소 등. 21~24는 비관광지</t>
+  </si>
+  <si>
+    <t>VISIT_AREA_TYPE_CD</t>
+  </si>
+  <si>
+    <t>체류 시간(분). 0분 이하 이상치 다수 존재 확인됨</t>
+  </si>
+  <si>
+    <t>RESIDENCE_TIME_MIN</t>
+  </si>
+  <si>
+    <t>관심지점(POI) 명칭 (결측률 54%대)</t>
+  </si>
+  <si>
+    <t>POI_NM</t>
+  </si>
+  <si>
+    <t>관심지점(POI) ID (결측률 54%대)</t>
+  </si>
+  <si>
+    <t>POI_ID</t>
+  </si>
+  <si>
+    <t>방문지 Y좌표(위도 계열)</t>
+  </si>
+  <si>
+    <t>Y_COORD</t>
+  </si>
+  <si>
+    <t>방문지 X좌표(경도 계열)</t>
+  </si>
+  <si>
+    <t>X_COORD</t>
+  </si>
+  <si>
+    <t>방문 종료 일시</t>
+  </si>
+  <si>
+    <t>VISIT_END_YMD</t>
+  </si>
+  <si>
+    <t>방문 시작 일시</t>
+  </si>
+  <si>
+    <t>VISIT_START_YMD</t>
+  </si>
+  <si>
+    <t>방문지명</t>
+  </si>
+  <si>
+    <t>해당 여행 내 방문 순서</t>
+  </si>
+  <si>
+    <t>VISIT_ORDER</t>
+  </si>
+  <si>
+    <t>방문지 고유 식별자. 활동/소비/이동/사진 테이블의 조인 키</t>
+  </si>
+  <si>
+    <t>tn_visit_area_info (방문지정보) — 방문지별 상세 기록 — 컬럼 설명</t>
+  </si>
+  <si>
+    <t>레코드 수정 일시, 대부분 결측</t>
+  </si>
+  <si>
+    <t>등간척도</t>
+  </si>
+  <si>
+    <t>연속형 (일시)</t>
+  </si>
+  <si>
+    <t>레코드 등록 일시(시스템 로그성 정보)</t>
+  </si>
+  <si>
+    <t>삭제 권한 설정값, 데이터 내용과 무관</t>
+  </si>
+  <si>
+    <t>명목척도</t>
+  </si>
+  <si>
+    <t>명목형</t>
+  </si>
+  <si>
+    <t>수정 권한 설정값, 데이터 내용과 무관</t>
+  </si>
+  <si>
+    <t>쓰기 권한 설정값, 데이터 내용과 무관</t>
+  </si>
+  <si>
+    <t>화면 표시 순서를 위한 관리용 값</t>
+  </si>
+  <si>
+    <t>서열척도</t>
+  </si>
+  <si>
+    <t>이산형 (표시 순서)</t>
+  </si>
+  <si>
+    <t>삭제 여부를 나타내는 시스템 관리용 플래그</t>
+  </si>
+  <si>
+    <t>명목형 (이진 플래그)</t>
+  </si>
+  <si>
+    <t>대부분 비어있는 메모 필드</t>
+  </si>
+  <si>
+    <t>명목형 (텍스트)</t>
+  </si>
+  <si>
+    <t>명목형 (텍스트 라벨)</t>
+  </si>
+  <si>
+    <t>시스템 내부 일련번호로 값 자체에 분석적 의미 없음</t>
+  </si>
+  <si>
+    <t>판단 근거(불필요/애매 사유)</t>
+  </si>
+  <si>
+    <t>척도분류</t>
+  </si>
+  <si>
+    <t>형태분류</t>
+  </si>
+  <si>
+    <t>애매(판단 보류)</t>
+  </si>
+  <si>
+    <t>●</t>
+  </si>
+  <si>
+    <t>분석에 불필요</t>
+  </si>
+  <si>
+    <t>리 단위 지명, 동 지역은 대부분 결측</t>
+  </si>
+  <si>
+    <t>SGG_CD를 구성하는 하위 코드, SGG_CD와 정보 중복</t>
+  </si>
+  <si>
+    <t>테이블별 결측률이 60~85%로 매우 높음</t>
+  </si>
+  <si>
+    <t>품목을 나열한 자유텍스트로 정형화되어 있지 않음</t>
+  </si>
+  <si>
+    <t>명목형 (자유텍스트)</t>
+  </si>
+  <si>
+    <t>비율척도</t>
+  </si>
+  <si>
+    <t>연속형 (금액, 절대 0 존재)</t>
+  </si>
+  <si>
+    <t>LOTNO_ADDR과 정보 중복, 결측률 높음</t>
+  </si>
+  <si>
+    <t>ROAD_NM_ADDR과 정보 중복, 결측률 높음</t>
+  </si>
+  <si>
+    <t>명목형 (텍스트 주소)</t>
+  </si>
+  <si>
+    <t>사업자등록번호로 STORE_NM과 식별 정보 중복, 분석 변수로 쓰기 어려움</t>
+  </si>
+  <si>
+    <t>명목형 (식별자)</t>
+  </si>
+  <si>
+    <t>코드북에 정의가 없어 정확한 의미 미확인 (1~22 분포만 확인됨)</t>
+  </si>
+  <si>
+    <t>이산형 (수량 추정, 의미 확인 필요)</t>
+  </si>
+  <si>
+    <t>같은 레코드 내 일련번호, 집계 시 불필요</t>
+  </si>
+  <si>
+    <t>이산형 (순번)</t>
+  </si>
+  <si>
+    <t>같은 레코드 내 순번, 집계 시 불필요</t>
+  </si>
+  <si>
+    <t>방문지 내 활동 순번, 집계 시 불필요</t>
+  </si>
+  <si>
+    <t>활동 유형 코드 (코드북 cd_a='ACT'). 예: 1=취식, 2=쇼핑/구매, 3=체험활동 등</t>
+  </si>
+  <si>
+    <t>체험/입장 구분, 결측이 많고 활용 범위가 좁음</t>
+  </si>
+  <si>
+    <t>명목형 (이진 성격)</t>
+  </si>
+  <si>
+    <t>지출 발생 방식 구분으로 활용 목적이 제한적</t>
+  </si>
+  <si>
+    <t>명목형 (이진)</t>
+  </si>
+  <si>
+    <t>자유 서술형 텍스트로 정형 분석에 부적합</t>
+  </si>
+  <si>
+    <t>활동유형이 '기타'일 때만 채워지는 자유텍스트</t>
+  </si>
+  <si>
+    <t>여행 내 사전소비 순번, 집계 시 불필요</t>
+  </si>
+  <si>
+    <t>서열형</t>
+  </si>
+  <si>
+    <t>여행 내 동반자 순번, 집계 시 불필요</t>
+  </si>
+  <si>
+    <t>숙소 방문 건에서만 값이 존재하는 구조적 결측</t>
+  </si>
+  <si>
+    <t>여행 내 숙박결제 순번, 집계 시 불필요</t>
+  </si>
+  <si>
+    <t>MVMN_SE 코드와 중복되는 텍스트</t>
+  </si>
+  <si>
+    <t>여행 내 결제 순번, 집계 시 불필요</t>
+  </si>
+  <si>
+    <t>방문지 좌표(Y_COORD)와 별도로 필요한지 불명확</t>
+  </si>
+  <si>
+    <t>연속형 (좌표, 임의 원점)</t>
+  </si>
+  <si>
+    <t>방문지 좌표(X_COORD)와 별도로 필요한지 불명확</t>
+  </si>
+  <si>
+    <t>사진 해상도, 분석 목적과 무관</t>
+  </si>
+  <si>
+    <t>파일 저장 경로 텍스트</t>
+  </si>
+  <si>
+    <t>사진 파일 포맷(jpg 등), 분석 목적과 무관</t>
+  </si>
+  <si>
+    <t>사진 파일명 텍스트</t>
+  </si>
+  <si>
+    <t>사진 파일 시스템 식별자</t>
+  </si>
+  <si>
+    <t>방문지 내 사진 순번, 집계 시 불필요</t>
+  </si>
+  <si>
+    <t>TRAVEL_MISSION의 확인값으로 추정되나 값 체계 미확인, 활용도 낮음</t>
+  </si>
+  <si>
+    <t>결측률 67%대이며 인코딩 체계 미확인</t>
+  </si>
+  <si>
+    <t>tn_move_his의 MVMN_CD와 중복되는 텍스트, 신뢰도 미검증</t>
+  </si>
+  <si>
+    <t>연속형 (일자)</t>
+  </si>
+  <si>
+    <t>값 체계(코드 or 텍스트)가 코드북에 없어 미확인</t>
+  </si>
+  <si>
+    <t>서열형 (1~5 리커트)</t>
+  </si>
+  <si>
+    <t>연속형 (시간(분), 절대 0 존재)</t>
+  </si>
+  <si>
+    <t>결측률 54%대</t>
   </si>
   <si>
     <t>TRAVEL_MISSION</t>
-  </si>
-  <si>
-    <t>여행 페르소나(텍스트/코드, 결측률 높음)</t>
-  </si>
-  <si>
-    <t>TRAVEL_PERSONA</t>
-  </si>
-  <si>
-    <t>주 이용 이동수단명(텍스트)</t>
-  </si>
-  <si>
-    <t>MVMN_NM</t>
-  </si>
-  <si>
-    <t>여행 종료일</t>
-  </si>
-  <si>
-    <t>TRAVEL_END_YMD</t>
-  </si>
-  <si>
-    <t>여행 시작일</t>
-  </si>
-  <si>
-    <t>TRAVEL_START_YMD</t>
-  </si>
-  <si>
-    <t>여행 목적(코드 또는 텍스트, 값 체계 확인 필요)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2C2C2A"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>여행</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2C2C2A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2C2C2A"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>중</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2C2C2A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2C2C2A"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수행</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2C2C2A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2C2C2A"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>미션</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2C2C2A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2C2C2A"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>코드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2C2C2A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2C2C2A"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>코드북</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2C2C2A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> cd_a='MIS'). </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2C2C2A"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>예</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2C2C2A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>: 1=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2C2C2A"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>쇼핑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2C2C2A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, 5=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2C2C2A"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>야외스포츠</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2C2C2A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, 9=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2C2C2A"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지역축제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2C2C2A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2C2C2A"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>참가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2C2C2A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2C2C2A"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>등</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2C2C2A"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>여행</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2C2C2A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2C2C2A"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>목적</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2C2C2A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2C2C2A"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>코드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2C2C2A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2C2C2A"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>또는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2C2C2A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2C2C2A"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>텍스트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2C2C2A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2C2C2A"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>값</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2C2C2A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2C2C2A"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>체계</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2C2C2A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2C2C2A"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>확인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2C2C2A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2C2C2A"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>필요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF2C2C2A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>TRAVEL_PURPOSE</t>
-  </si>
-  <si>
-    <t>여행자 식별자. tn_traveller_master.TRAVELER_ID와 조인</t>
-  </si>
-  <si>
-    <t>TRAVELER_ID</t>
-  </si>
-  <si>
-    <t>여행명(자유 텍스트)</t>
-  </si>
-  <si>
-    <t>TRAVEL_NM</t>
-  </si>
-  <si>
-    <t>여행 고유 식별자. 다른 모든 여행 단위 테이블의 조인 키</t>
-  </si>
-  <si>
-    <t>tn_travel (여행) — 여행 단위 마스터 — 컬럼 설명</t>
-  </si>
-  <si>
-    <t>본인을 제외한 동반자 수(응답자 기재값)</t>
-  </si>
-  <si>
-    <t>TRAVEL_COMPANIONS_NUM</t>
-  </si>
-  <si>
-    <t>여행 동기 코드 3순위 (코드북 cd_a='TMT')</t>
-  </si>
-  <si>
-    <t>TRAVEL_MOTIVE_3</t>
-  </si>
-  <si>
-    <t>여행 동기 코드 2순위 (코드북 cd_a='TMT')</t>
-  </si>
-  <si>
-    <t>TRAVEL_MOTIVE_2</t>
-  </si>
-  <si>
-    <t>여행 동기 코드 1순위 (코드북 cd_a='TMT')</t>
-  </si>
-  <si>
-    <t>TRAVEL_MOTIVE_1</t>
-  </si>
-  <si>
-    <t>여행 기간(시작~종료일 텍스트)</t>
-  </si>
-  <si>
-    <t>TRAVEL_STATUS_YMD</t>
-  </si>
-  <si>
-    <t>동반유형 요약(텍스트). 예: 나홀로 여행, 2인 가족 여행, 자녀 동반 여행 등 — tn_companion_info의 실제 동반자 수와 불일치 사례가 있음을 EDA에서 확인</t>
-  </si>
-  <si>
-    <t>TRAVEL_STATUS_ACCOMPANY</t>
-  </si>
-  <si>
-    <t>여행 목적지(시/도 단위 텍스트)</t>
-  </si>
-  <si>
-    <t>TRAVEL_STATUS_DESTINATION</t>
-  </si>
-  <si>
-    <t>여행 당시 거주지(시/도 단위 텍스트)</t>
-  </si>
-  <si>
-    <t>TRAVEL_STATUS_RESIDENCE</t>
-  </si>
-  <si>
-    <t>여행스타일 축8 (1~7 척도)</t>
-  </si>
-  <si>
-    <t>TRAVEL_STYL_8</t>
-  </si>
-  <si>
-    <t>여행스타일 축7 (1~7 척도)</t>
-  </si>
-  <si>
-    <t>TRAVEL_STYL_7</t>
-  </si>
-  <si>
-    <t>여행스타일 축6 (1~7 척도)</t>
-  </si>
-  <si>
-    <t>TRAVEL_STYL_6</t>
-  </si>
-  <si>
-    <t>여행스타일 축5 (1~7 척도)</t>
-  </si>
-  <si>
-    <t>TRAVEL_STYL_5</t>
-  </si>
-  <si>
-    <t>여행스타일 축4 (1~7 척도)</t>
-  </si>
-  <si>
-    <t>TRAVEL_STYL_4</t>
-  </si>
-  <si>
-    <t>여행스타일 축3 (1~7 척도)</t>
-  </si>
-  <si>
-    <t>TRAVEL_STYL_3</t>
-  </si>
-  <si>
-    <t>여행스타일 축2 (1~7 척도, 축 주제는 설문 문항 원문 확인 필요)</t>
-  </si>
-  <si>
-    <t>TRAVEL_STYL_2</t>
-  </si>
-  <si>
-    <t>여행스타일 축1: 자연(1) ↔ 도시(7) 선호도 (코드북 cd_a='TSY', 1~7 척도)</t>
-  </si>
-  <si>
-    <t>TRAVEL_STYL_1</t>
-  </si>
-  <si>
-    <t>선호 여행지 시군구 코드 3순위</t>
-  </si>
-  <si>
-    <t>TRAVEL_LIKE_SGG_3</t>
-  </si>
-  <si>
-    <t>선호 여행지 시/도 코드 3순위</t>
-  </si>
-  <si>
-    <t>TRAVEL_LIKE_SIDO_3</t>
-  </si>
-  <si>
-    <t>선호 여행지 시군구 코드 2순위</t>
-  </si>
-  <si>
-    <t>TRAVEL_LIKE_SGG_2</t>
-  </si>
-  <si>
-    <t>선호 여행지 시/도 코드 2순위</t>
-  </si>
-  <si>
-    <t>TRAVEL_LIKE_SIDO_2</t>
-  </si>
-  <si>
-    <t>선호 여행지 시군구 코드 1순위</t>
-  </si>
-  <si>
-    <t>TRAVEL_LIKE_SGG_1</t>
-  </si>
-  <si>
-    <t>선호 여행지 시/도 코드 1순위 (코드북 cd_a='TAR')</t>
-  </si>
-  <si>
-    <t>TRAVEL_LIKE_SIDO_1</t>
-  </si>
-  <si>
-    <t>최근 기간 내 여행 횟수</t>
-  </si>
-  <si>
-    <t>TRAVEL_NUM</t>
-  </si>
-  <si>
-    <t>여행 빈도_기간 코드 (코드북 cd_a='TTM'). 1=1주일, 2=한달, 3=1년 등</t>
-  </si>
-  <si>
-    <t>TRAVEL_TERM</t>
-  </si>
-  <si>
-    <t>가구소득 구간 코드 (코드북 cd_a='INC')</t>
-  </si>
-  <si>
-    <t>HOUSE_INCOME</t>
-  </si>
-  <si>
-    <t>개인소득 구간 코드 (코드북 cd_a='INC', 1~12 구간)</t>
-  </si>
-  <si>
-    <t>INCOME</t>
-  </si>
-  <si>
-    <t>직업이 '기타'일 때의 상세 텍스트(결측률 매우 높음, 95%대)</t>
-  </si>
-  <si>
-    <t>JOB_ETC</t>
-  </si>
-  <si>
-    <t>직업 코드 (코드북 cd_a='JOB')</t>
-  </si>
-  <si>
-    <t>JOB_NM</t>
-  </si>
-  <si>
-    <t>가족 구성원 수</t>
-  </si>
-  <si>
-    <t>FAMILY_MEMB</t>
-  </si>
-  <si>
-    <t>혼인상태 코드 (코드북 cd_a='MAR')</t>
-  </si>
-  <si>
-    <t>MARR_STTS</t>
-  </si>
-  <si>
-    <t>최종학력 이수 여부 코드 (코드북 cd_a='EFS')</t>
-  </si>
-  <si>
-    <t>EDU_FNSH_SE</t>
-  </si>
-  <si>
-    <t>최종학력 코드 (코드북 cd_a='EDU')</t>
-  </si>
-  <si>
-    <t>EDU_NM</t>
-  </si>
-  <si>
-    <t>연령대(10대 단위, 예: 20/30/40/50/60)</t>
-  </si>
-  <si>
-    <t>AGE_GRP</t>
-  </si>
-  <si>
-    <t>성별</t>
-  </si>
-  <si>
-    <t>GENDER</t>
-  </si>
-  <si>
-    <t>거주지 시군구 코드. tc_sgg와 조인</t>
-  </si>
-  <si>
-    <t>RESIDENCE_SGG_CD</t>
-  </si>
-  <si>
-    <t>여행객 고유 식별자. tn_travel.TRAVELER_ID와 조인</t>
-  </si>
-  <si>
-    <t>tn_traveller_master (여행객 Master) — 여행객 인구통계·성향 마스터 — 컬럼 설명</t>
-  </si>
-  <si>
-    <t>방문지의 시군구 코드. tc_sgg와 조인 (결측률 높음)</t>
-  </si>
-  <si>
-    <t>추천 의향 점수 (코드북 cd_a='REC', 1~5점)</t>
-  </si>
-  <si>
-    <t>RCMDTN_INTENTION</t>
-  </si>
-  <si>
-    <t>재방문 의향 점수 (코드북 cd_a='REP', 1~5점)</t>
-  </si>
-  <si>
-    <t>REVISIT_INTENTION</t>
-  </si>
-  <si>
-    <t>전반적 만족도 점수 (코드북 cd_a='DGS', 1~5점). 비관광지(21~24)는 결측률 74%</t>
-  </si>
-  <si>
-    <t>DGSTFN</t>
-  </si>
-  <si>
-    <t>숙소 유형 코드 (코드북 cd_a='HTY', 방문지 유형이 숙소인 경우만 값 존재)</t>
-  </si>
-  <si>
-    <t>방문 선택 이유 코드 (코드북 cd_a='REN'). 1=지명도/핫플레이스, 5=지인 추천 등</t>
-  </si>
-  <si>
-    <t>VISIT_CHC_REASON_CD</t>
-  </si>
-  <si>
-    <t>재방문 여부 코드 (코드북 cd_a='REV'). 1=처음 방문, 2=재방문</t>
-  </si>
-  <si>
-    <t>REVISIT_YN</t>
-  </si>
-  <si>
-    <t>방문지 유형 코드 (코드북 cd_a='VIS'). 1=자연관광지, 4=상업지구, 11=식당/카페, 21=집, 22=친구/친지집, 23=사무실, 24=숙소 등. 21~24는 비관광지</t>
-  </si>
-  <si>
-    <t>VISIT_AREA_TYPE_CD</t>
-  </si>
-  <si>
-    <t>체류 시간(분). 0분 이하 이상치 다수 존재 확인됨</t>
-  </si>
-  <si>
-    <t>RESIDENCE_TIME_MIN</t>
-  </si>
-  <si>
-    <t>관심지점(POI) 명칭 (결측률 54%대)</t>
-  </si>
-  <si>
-    <t>POI_NM</t>
-  </si>
-  <si>
-    <t>관심지점(POI) ID (결측률 54%대)</t>
-  </si>
-  <si>
-    <t>POI_ID</t>
-  </si>
-  <si>
-    <t>방문지 Y좌표(위도 계열)</t>
-  </si>
-  <si>
-    <t>Y_COORD</t>
-  </si>
-  <si>
-    <t>방문지 X좌표(경도 계열)</t>
-  </si>
-  <si>
-    <t>X_COORD</t>
-  </si>
-  <si>
-    <t>방문 종료 일시</t>
-  </si>
-  <si>
-    <t>VISIT_END_YMD</t>
-  </si>
-  <si>
-    <t>방문 시작 일시</t>
-  </si>
-  <si>
-    <t>VISIT_START_YMD</t>
-  </si>
-  <si>
-    <t>방문지명</t>
-  </si>
-  <si>
-    <t>해당 여행 내 방문 순서</t>
-  </si>
-  <si>
-    <t>VISIT_ORDER</t>
-  </si>
-  <si>
-    <t>방문지 고유 식별자. 활동/소비/이동/사진 테이블의 조인 키</t>
-  </si>
-  <si>
-    <t>tn_visit_area_info (방문지정보) — 방문지별 상세 기록 — 컬럼 설명</t>
-  </si>
-  <si>
-    <t>레코드 수정 일시, 대부분 결측</t>
-  </si>
-  <si>
-    <t>등간척도</t>
-  </si>
-  <si>
-    <t>연속형 (일시)</t>
-  </si>
-  <si>
-    <t>레코드 등록 일시(시스템 로그성 정보)</t>
-  </si>
-  <si>
-    <t>삭제 권한 설정값, 데이터 내용과 무관</t>
-  </si>
-  <si>
-    <t>명목척도</t>
-  </si>
-  <si>
-    <t>명목형</t>
-  </si>
-  <si>
-    <t>수정 권한 설정값, 데이터 내용과 무관</t>
-  </si>
-  <si>
-    <t>쓰기 권한 설정값, 데이터 내용과 무관</t>
-  </si>
-  <si>
-    <t>화면 표시 순서를 위한 관리용 값</t>
-  </si>
-  <si>
-    <t>서열척도</t>
-  </si>
-  <si>
-    <t>이산형 (표시 순서)</t>
-  </si>
-  <si>
-    <t>삭제 여부를 나타내는 시스템 관리용 플래그</t>
-  </si>
-  <si>
-    <t>명목형 (이진 플래그)</t>
-  </si>
-  <si>
-    <t>대부분 비어있는 메모 필드</t>
-  </si>
-  <si>
-    <t>명목형 (텍스트)</t>
-  </si>
-  <si>
-    <t>명목형 (텍스트 라벨)</t>
-  </si>
-  <si>
-    <t>시스템 내부 일련번호로 값 자체에 분석적 의미 없음</t>
-  </si>
-  <si>
-    <t>판단 근거(불필요/애매 사유)</t>
-  </si>
-  <si>
-    <t>척도분류</t>
-  </si>
-  <si>
-    <t>형태분류</t>
-  </si>
-  <si>
-    <t>애매(판단 보류)</t>
-  </si>
-  <si>
-    <t>●</t>
-  </si>
-  <si>
-    <t>분석에 불필요</t>
-  </si>
-  <si>
-    <t>리 단위 지명, 동 지역은 대부분 결측</t>
-  </si>
-  <si>
-    <t>SGG_CD를 구성하는 하위 코드, SGG_CD와 정보 중복</t>
-  </si>
-  <si>
-    <t>테이블별 결측률이 60~85%로 매우 높음</t>
-  </si>
-  <si>
-    <t>품목을 나열한 자유텍스트로 정형화되어 있지 않음</t>
-  </si>
-  <si>
-    <t>명목형 (자유텍스트)</t>
-  </si>
-  <si>
-    <t>비율척도</t>
-  </si>
-  <si>
-    <t>연속형 (금액, 절대 0 존재)</t>
-  </si>
-  <si>
-    <t>LOTNO_ADDR과 정보 중복, 결측률 높음</t>
-  </si>
-  <si>
-    <t>ROAD_NM_ADDR과 정보 중복, 결측률 높음</t>
-  </si>
-  <si>
-    <t>명목형 (텍스트 주소)</t>
-  </si>
-  <si>
-    <t>사업자등록번호로 STORE_NM과 식별 정보 중복, 분석 변수로 쓰기 어려움</t>
-  </si>
-  <si>
-    <t>명목형 (식별자)</t>
-  </si>
-  <si>
-    <t>코드북에 정의가 없어 정확한 의미 미확인 (1~22 분포만 확인됨)</t>
-  </si>
-  <si>
-    <t>이산형 (수량 추정, 의미 확인 필요)</t>
-  </si>
-  <si>
-    <t>같은 레코드 내 일련번호, 집계 시 불필요</t>
-  </si>
-  <si>
-    <t>이산형 (순번)</t>
-  </si>
-  <si>
-    <t>같은 레코드 내 순번, 집계 시 불필요</t>
-  </si>
-  <si>
-    <t>방문지 내 활동 순번, 집계 시 불필요</t>
-  </si>
-  <si>
-    <t>활동 유형 코드 (코드북 cd_a='ACT'). 예: 1=취식, 2=쇼핑/구매, 3=체험활동 등</t>
-  </si>
-  <si>
-    <t>체험/입장 구분, 결측이 많고 활용 범위가 좁음</t>
-  </si>
-  <si>
-    <t>명목형 (이진 성격)</t>
-  </si>
-  <si>
-    <t>지출 발생 방식 구분으로 활용 목적이 제한적</t>
-  </si>
-  <si>
-    <t>명목형 (이진)</t>
-  </si>
-  <si>
-    <t>자유 서술형 텍스트로 정형 분석에 부적합</t>
-  </si>
-  <si>
-    <t>활동유형이 '기타'일 때만 채워지는 자유텍스트</t>
-  </si>
-  <si>
-    <t>여행 내 사전소비 순번, 집계 시 불필요</t>
-  </si>
-  <si>
-    <t>서열형</t>
-  </si>
-  <si>
-    <t>여행 내 동반자 순번, 집계 시 불필요</t>
-  </si>
-  <si>
-    <t>숙소 방문 건에서만 값이 존재하는 구조적 결측</t>
-  </si>
-  <si>
-    <t>여행 내 숙박결제 순번, 집계 시 불필요</t>
-  </si>
-  <si>
-    <t>MVMN_SE 코드와 중복되는 텍스트</t>
-  </si>
-  <si>
-    <t>여행 내 결제 순번, 집계 시 불필요</t>
-  </si>
-  <si>
-    <t>방문지 좌표(Y_COORD)와 별도로 필요한지 불명확</t>
-  </si>
-  <si>
-    <t>연속형 (좌표, 임의 원점)</t>
-  </si>
-  <si>
-    <t>방문지 좌표(X_COORD)와 별도로 필요한지 불명확</t>
-  </si>
-  <si>
-    <t>사진 해상도, 분석 목적과 무관</t>
-  </si>
-  <si>
-    <t>파일 저장 경로 텍스트</t>
-  </si>
-  <si>
-    <t>사진 파일 포맷(jpg 등), 분석 목적과 무관</t>
-  </si>
-  <si>
-    <t>사진 파일명 텍스트</t>
-  </si>
-  <si>
-    <t>사진 파일 시스템 식별자</t>
-  </si>
-  <si>
-    <t>방문지 내 사진 순번, 집계 시 불필요</t>
-  </si>
-  <si>
-    <t>TRAVEL_MISSION의 확인값으로 추정되나 값 체계 미확인, 활용도 낮음</t>
-  </si>
-  <si>
-    <t>결측률 67%대이며 인코딩 체계 미확인</t>
-  </si>
-  <si>
-    <t>tn_move_his의 MVMN_CD와 중복되는 텍스트, 신뢰도 미검증</t>
-  </si>
-  <si>
-    <t>연속형 (일자)</t>
-  </si>
-  <si>
-    <t>값 체계(코드 or 텍스트)가 코드북에 없어 미확인</t>
-  </si>
-  <si>
-    <t>서열형 (1~5 리커트)</t>
-  </si>
-  <si>
-    <t>연속형 (시간(분), 절대 0 존재)</t>
-  </si>
-  <si>
-    <t>결측률 54%대</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1283,6 +1675,20 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF2C2C2A"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF2C2C2A"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -1352,7 +1758,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1425,6 +1831,12 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1769,7 +2181,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{889CC51F-B207-42A8-84AE-4F4786EC7B3C}">
   <dimension ref="B2:G16"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="6" style="1" customWidth="1"/>
@@ -1781,26 +2193,26 @@
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:7" ht="21" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B3" s="16" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B4" s="5" t="s">
         <v>26</v>
       </c>
@@ -1811,16 +2223,16 @@
         <v>24</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="11">
         <v>1</v>
       </c>
@@ -1831,16 +2243,16 @@
         <v>22</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="4">
         <v>2</v>
       </c>
@@ -1851,14 +2263,14 @@
         <v>20</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G6" s="12"/>
     </row>
-    <row r="7" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="4">
         <v>3</v>
       </c>
@@ -1869,14 +2281,14 @@
         <v>18</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G7" s="12"/>
     </row>
-    <row r="8" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="11">
         <v>4</v>
       </c>
@@ -1887,16 +2299,16 @@
         <v>16</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="11">
         <v>5</v>
       </c>
@@ -1907,16 +2319,16 @@
         <v>14</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="11">
         <v>6</v>
       </c>
@@ -1927,16 +2339,16 @@
         <v>12</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="11">
         <v>7</v>
       </c>
@@ -1947,16 +2359,16 @@
         <v>10</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="11">
         <v>8</v>
       </c>
@@ -1967,16 +2379,16 @@
         <v>8</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11">
         <v>9</v>
       </c>
@@ -1987,16 +2399,16 @@
         <v>6</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="11">
         <v>10</v>
       </c>
@@ -2007,16 +2419,16 @@
         <v>4</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="11">
         <v>11</v>
       </c>
@@ -2027,16 +2439,16 @@
         <v>2</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" s="11">
         <v>12</v>
       </c>
@@ -2047,13 +2459,13 @@
         <v>0</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>
@@ -2065,7 +2477,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30C2FC44-6B8A-42A7-BB4D-E79341202999}">
   <dimension ref="B2:G17"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="6" style="1" customWidth="1"/>
@@ -2077,26 +2489,26 @@
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:7" ht="21" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B3" s="16" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B4" s="5" t="s">
         <v>26</v>
       </c>
@@ -2107,16 +2519,16 @@
         <v>24</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="4">
         <v>1</v>
       </c>
@@ -2127,14 +2539,14 @@
         <v>86</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G5" s="12"/>
     </row>
-    <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="4">
         <v>2</v>
       </c>
@@ -2145,14 +2557,14 @@
         <v>162</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G6" s="12"/>
     </row>
-    <row r="7" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="4">
         <v>3</v>
       </c>
@@ -2163,14 +2575,14 @@
         <v>160</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G7" s="12"/>
     </row>
-    <row r="8" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="11">
         <v>4</v>
       </c>
@@ -2181,16 +2593,16 @@
         <v>158</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="21">
         <v>5</v>
       </c>
@@ -2201,16 +2613,16 @@
         <v>156</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="4">
         <v>6</v>
       </c>
@@ -2221,14 +2633,14 @@
         <v>93</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G10" s="12"/>
     </row>
-    <row r="11" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="21">
         <v>7</v>
       </c>
@@ -2239,16 +2651,16 @@
         <v>128</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="11">
         <v>8</v>
       </c>
@@ -2259,16 +2671,16 @@
         <v>109</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="4">
         <v>9</v>
       </c>
@@ -2279,14 +2691,14 @@
         <v>155</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G13" s="12"/>
     </row>
-    <row r="14" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="4">
         <v>10</v>
       </c>
@@ -2297,14 +2709,14 @@
         <v>61</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G14" s="12"/>
     </row>
-    <row r="15" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="4">
         <v>11</v>
       </c>
@@ -2315,14 +2727,14 @@
         <v>104</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G15" s="12"/>
     </row>
-    <row r="16" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" s="4">
         <v>12</v>
       </c>
@@ -2333,14 +2745,14 @@
         <v>57</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G16" s="12"/>
     </row>
-    <row r="17" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="21">
         <v>13</v>
       </c>
@@ -2351,13 +2763,13 @@
         <v>103</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -2369,7 +2781,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8853F1A0-3D5F-41EF-B101-0242908DA680}">
   <dimension ref="B2:G16"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="6" style="1" customWidth="1"/>
@@ -2381,26 +2793,26 @@
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:7" ht="21" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B3" s="16" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B4" s="5" t="s">
         <v>26</v>
       </c>
@@ -2411,16 +2823,16 @@
         <v>24</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="4">
         <v>1</v>
       </c>
@@ -2431,14 +2843,14 @@
         <v>86</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G5" s="12"/>
     </row>
-    <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="4">
         <v>2</v>
       </c>
@@ -2449,14 +2861,14 @@
         <v>84</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G6" s="12"/>
     </row>
-    <row r="7" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="11">
         <v>3</v>
       </c>
@@ -2467,16 +2879,16 @@
         <v>183</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="11">
         <v>4</v>
       </c>
@@ -2487,16 +2899,16 @@
         <v>181</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="11">
         <v>5</v>
       </c>
@@ -2507,16 +2919,16 @@
         <v>179</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="11">
         <v>6</v>
       </c>
@@ -2527,16 +2939,16 @@
         <v>177</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="4">
         <v>7</v>
       </c>
@@ -2547,14 +2959,14 @@
         <v>175</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G11" s="12"/>
     </row>
-    <row r="12" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="11">
         <v>8</v>
       </c>
@@ -2565,16 +2977,16 @@
         <v>173</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11">
         <v>9</v>
       </c>
@@ -2585,16 +2997,16 @@
         <v>171</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="21">
         <v>10</v>
       </c>
@@ -2605,16 +3017,16 @@
         <v>169</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="F14" s="18" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="21">
         <v>11</v>
       </c>
@@ -2625,16 +3037,16 @@
         <v>167</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" s="4">
         <v>12</v>
       </c>
@@ -2645,10 +3057,10 @@
         <v>165</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G16" s="12"/>
     </row>
@@ -2661,7 +3073,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E377995E-56EA-41BD-B824-1938DCFBF51B}">
   <dimension ref="B2:G14"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="6" style="1" customWidth="1"/>
@@ -2673,26 +3085,26 @@
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:7" ht="21" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B3" s="16" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B4" s="5" t="s">
         <v>26</v>
       </c>
@@ -2703,16 +3115,16 @@
         <v>24</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="4">
         <v>1</v>
       </c>
@@ -2720,167 +3132,167 @@
         <v>87</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G5" s="12"/>
     </row>
-    <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="4">
         <v>2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G6" s="12"/>
     </row>
-    <row r="7" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="4">
         <v>3</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G7" s="12"/>
     </row>
-    <row r="8" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="21">
         <v>4</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>198</v>
+        <v>383</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>382</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="4">
         <v>5</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G9" s="12"/>
     </row>
-    <row r="10" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="4">
         <v>6</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G10" s="12"/>
     </row>
-    <row r="11" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="21">
         <v>7</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="21">
         <v>8</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="4">
         <v>9</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>188</v>
+        <v>380</v>
+      </c>
+      <c r="D13" s="28" t="s">
+        <v>381</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G13" s="12"/>
     </row>
-    <row r="14" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="11">
         <v>10</v>
       </c>
@@ -2891,13 +3303,13 @@
         <v>186</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -2909,21 +3321,21 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B824040F-91B4-4781-8D7F-6CF474419604}">
   <dimension ref="B2:D40"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="6" style="1" customWidth="1"/>
     <col min="3" max="3" width="30" style="1" customWidth="1"/>
     <col min="4" max="4" width="95" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.75" style="1"/>
+    <col min="5" max="16384" width="8.69921875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:4" ht="21" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B4" s="5" t="s">
         <v>26</v>
       </c>
@@ -2934,400 +3346,400 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="4">
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="4">
         <v>2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="4">
         <v>3</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="4">
         <v>4</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="4">
         <v>5</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="22">
         <v>6</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="4">
         <v>7</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="4">
         <v>8</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="13" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="4">
         <v>9</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="14" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="25">
         <v>10</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="15" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="4">
         <v>11</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="16" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" s="4">
         <v>12</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="4">
         <v>13</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="4">
         <v>14</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B19" s="22">
         <v>15</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B20" s="22">
         <v>16</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B21" s="22">
         <v>17</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="22">
         <v>18</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="22">
         <v>19</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="22">
         <v>20</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="25" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="4">
         <v>21</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="26" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="4">
         <v>22</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="27" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="4">
         <v>23</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="28" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="4">
         <v>24</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="29" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="4">
         <v>25</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="30" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B30" s="4">
         <v>26</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="31" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B31" s="4">
         <v>27</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="32" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="4">
         <v>28</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="33" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="22">
         <v>29</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="34" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B34" s="22">
         <v>30</v>
       </c>
       <c r="C34" s="23" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D34" s="24" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="35" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B35" s="4">
         <v>31</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="36" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B36" s="25">
         <v>32</v>
       </c>
       <c r="C36" s="26" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D36" s="27" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="37" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B37" s="22">
         <v>33</v>
       </c>
       <c r="C37" s="23" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D37" s="24" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="38" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="22">
         <v>34</v>
       </c>
       <c r="C38" s="23" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D38" s="24" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="39" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B39" s="22">
         <v>35</v>
       </c>
       <c r="C39" s="23" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D39" s="24" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="40" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B40" s="4">
         <v>36</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -3339,7 +3751,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFB60540-5D2D-4388-9F66-D0BEE907B1CB}">
   <dimension ref="B2:G27"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="6" style="1" customWidth="1"/>
@@ -3351,26 +3763,26 @@
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:7" ht="21" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B3" s="16" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B4" s="5" t="s">
         <v>26</v>
       </c>
@@ -3381,16 +3793,16 @@
         <v>24</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="4">
         <v>1</v>
       </c>
@@ -3398,17 +3810,17 @@
         <v>85</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G5" s="12"/>
     </row>
-    <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="4">
         <v>2</v>
       </c>
@@ -3419,32 +3831,32 @@
         <v>86</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G6" s="12"/>
     </row>
-    <row r="7" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="4">
         <v>3</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="G7" s="12"/>
     </row>
-    <row r="8" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="4">
         <v>4</v>
       </c>
@@ -3452,53 +3864,53 @@
         <v>166</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G8" s="12"/>
     </row>
-    <row r="9" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="4">
         <v>5</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G9" s="12"/>
     </row>
-    <row r="10" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="4">
         <v>6</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G10" s="12"/>
     </row>
-    <row r="11" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="4">
         <v>7</v>
       </c>
@@ -3509,14 +3921,14 @@
         <v>69</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G11" s="12"/>
     </row>
-    <row r="12" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="4">
         <v>8</v>
       </c>
@@ -3527,50 +3939,50 @@
         <v>67</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G12" s="12"/>
     </row>
-    <row r="13" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="4">
         <v>9</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G13" s="12"/>
     </row>
-    <row r="14" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="4">
         <v>10</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G14" s="12"/>
     </row>
-    <row r="15" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="11">
         <v>11</v>
       </c>
@@ -3581,16 +3993,16 @@
         <v>65</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" s="11">
         <v>12</v>
       </c>
@@ -3601,128 +4013,128 @@
         <v>63</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="21">
         <v>13</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="21">
         <v>14</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F18" s="18" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B19" s="4">
         <v>15</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G19" s="12"/>
     </row>
-    <row r="20" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B20" s="4">
         <v>16</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G20" s="12"/>
     </row>
-    <row r="21" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B21" s="4">
         <v>17</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G21" s="12"/>
     </row>
-    <row r="22" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="4">
         <v>18</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G22" s="12"/>
     </row>
-    <row r="23" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="21">
         <v>19</v>
       </c>
@@ -3730,73 +4142,73 @@
         <v>134</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="4">
         <v>20</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="G24" s="12"/>
     </row>
-    <row r="25" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="4">
         <v>21</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="G25" s="12"/>
     </row>
-    <row r="26" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="4">
         <v>22</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="G26" s="12"/>
     </row>
-    <row r="27" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="21">
         <v>23</v>
       </c>
@@ -3804,16 +4216,16 @@
         <v>52</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F27" s="18" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G27" s="17" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
   </sheetData>
@@ -3825,7 +4237,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{388C9CB8-6551-48BE-BDB5-28C0991C66C7}">
   <dimension ref="B2:G14"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="6" style="1" customWidth="1"/>
@@ -3837,26 +4249,26 @@
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:7" ht="21" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B3" s="16" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B4" s="5" t="s">
         <v>26</v>
       </c>
@@ -3867,16 +4279,16 @@
         <v>24</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="11">
         <v>1</v>
       </c>
@@ -3887,16 +4299,16 @@
         <v>22</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="4">
         <v>2</v>
       </c>
@@ -3907,14 +4319,14 @@
         <v>33</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G6" s="12"/>
     </row>
-    <row r="7" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="4">
         <v>3</v>
       </c>
@@ -3925,14 +4337,14 @@
         <v>31</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G7" s="12"/>
     </row>
-    <row r="8" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="4">
         <v>4</v>
       </c>
@@ -3943,14 +4355,14 @@
         <v>30</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G8" s="12"/>
     </row>
-    <row r="9" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="11">
         <v>5</v>
       </c>
@@ -3961,16 +4373,16 @@
         <v>29</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="11">
         <v>6</v>
       </c>
@@ -3981,16 +4393,16 @@
         <v>14</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="11">
         <v>7</v>
       </c>
@@ -4001,16 +4413,16 @@
         <v>12</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="11">
         <v>8</v>
       </c>
@@ -4021,16 +4433,16 @@
         <v>10</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11">
         <v>9</v>
       </c>
@@ -4041,16 +4453,16 @@
         <v>2</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="11">
         <v>10</v>
       </c>
@@ -4061,13 +4473,13 @@
         <v>28</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>
@@ -4079,7 +4491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA67096B-B088-4011-8F9A-EF6EF34D4A02}">
   <dimension ref="B2:G13"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="6" style="1" customWidth="1"/>
@@ -4091,26 +4503,26 @@
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:7" ht="21" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B3" s="16" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B4" s="5" t="s">
         <v>26</v>
       </c>
@@ -4121,16 +4533,16 @@
         <v>24</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="21">
         <v>1</v>
       </c>
@@ -4141,16 +4553,16 @@
         <v>51</v>
       </c>
       <c r="E5" s="18" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="11">
         <v>2</v>
       </c>
@@ -4161,16 +4573,16 @@
         <v>49</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="11">
         <v>3</v>
       </c>
@@ -4181,16 +4593,16 @@
         <v>47</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="11">
         <v>4</v>
       </c>
@@ -4201,16 +4613,16 @@
         <v>45</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="11">
         <v>5</v>
       </c>
@@ -4221,16 +4633,16 @@
         <v>43</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="4">
         <v>6</v>
       </c>
@@ -4241,14 +4653,14 @@
         <v>41</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G10" s="12"/>
     </row>
-    <row r="11" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="4">
         <v>7</v>
       </c>
@@ -4259,14 +4671,14 @@
         <v>39</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G11" s="12"/>
     </row>
-    <row r="12" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="4">
         <v>8</v>
       </c>
@@ -4277,14 +4689,14 @@
         <v>37</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G12" s="12"/>
     </row>
-    <row r="13" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="21">
         <v>9</v>
       </c>
@@ -4295,13 +4707,13 @@
         <v>35</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
     </row>
   </sheetData>
@@ -4313,7 +4725,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90AA2D68-1D96-49A7-9349-D3C1724B14E7}">
   <dimension ref="B2:G22"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="6" style="1" customWidth="1"/>
@@ -4325,26 +4737,26 @@
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:7" ht="21" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B3" s="16" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B4" s="5" t="s">
         <v>26</v>
       </c>
@@ -4355,16 +4767,16 @@
         <v>24</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="4">
         <v>1</v>
       </c>
@@ -4375,14 +4787,14 @@
         <v>86</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G5" s="12"/>
     </row>
-    <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="4">
         <v>2</v>
       </c>
@@ -4393,14 +4805,14 @@
         <v>84</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G6" s="12"/>
     </row>
-    <row r="7" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="4">
         <v>3</v>
       </c>
@@ -4408,17 +4820,17 @@
         <v>83</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G7" s="12"/>
     </row>
-    <row r="8" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="11">
         <v>4</v>
       </c>
@@ -4429,16 +4841,16 @@
         <v>81</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="11">
         <v>5</v>
       </c>
@@ -4449,16 +4861,16 @@
         <v>79</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="11">
         <v>6</v>
       </c>
@@ -4469,16 +4881,16 @@
         <v>77</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="21">
         <v>7</v>
       </c>
@@ -4489,16 +4901,16 @@
         <v>75</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="11">
         <v>8</v>
       </c>
@@ -4509,16 +4921,16 @@
         <v>73</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="4">
         <v>9</v>
       </c>
@@ -4529,14 +4941,14 @@
         <v>71</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G13" s="12"/>
     </row>
-    <row r="14" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="4">
         <v>10</v>
       </c>
@@ -4547,14 +4959,14 @@
         <v>69</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G14" s="12"/>
     </row>
-    <row r="15" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="4">
         <v>11</v>
       </c>
@@ -4565,14 +4977,14 @@
         <v>67</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G15" s="12"/>
     </row>
-    <row r="16" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" s="11">
         <v>12</v>
       </c>
@@ -4583,16 +4995,16 @@
         <v>65</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="11">
         <v>13</v>
       </c>
@@ -4603,16 +5015,16 @@
         <v>63</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="4">
         <v>14</v>
       </c>
@@ -4623,14 +5035,14 @@
         <v>61</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G18" s="12"/>
     </row>
-    <row r="19" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B19" s="4">
         <v>15</v>
       </c>
@@ -4641,14 +5053,14 @@
         <v>59</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G19" s="12"/>
     </row>
-    <row r="20" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B20" s="4">
         <v>16</v>
       </c>
@@ -4659,14 +5071,14 @@
         <v>57</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G20" s="12"/>
     </row>
-    <row r="21" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B21" s="21">
         <v>17</v>
       </c>
@@ -4677,16 +5089,16 @@
         <v>55</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="F21" s="18" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="21">
         <v>18</v>
       </c>
@@ -4697,13 +5109,13 @@
         <v>54</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F22" s="18" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
   </sheetData>
@@ -4715,7 +5127,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E1E5F2C-4A54-471E-A044-B2E858564189}">
   <dimension ref="B2:G13"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="6" style="1" customWidth="1"/>
@@ -4727,26 +5139,26 @@
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:7" ht="21" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B3" s="16" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B4" s="5" t="s">
         <v>26</v>
       </c>
@@ -4757,16 +5169,16 @@
         <v>24</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="4">
         <v>1</v>
       </c>
@@ -4777,14 +5189,14 @@
         <v>86</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G5" s="12"/>
     </row>
-    <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="4">
         <v>2</v>
       </c>
@@ -4795,14 +5207,14 @@
         <v>84</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G6" s="12"/>
     </row>
-    <row r="7" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="4">
         <v>3</v>
       </c>
@@ -4813,14 +5225,14 @@
         <v>100</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G7" s="12"/>
     </row>
-    <row r="8" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="11">
         <v>4</v>
       </c>
@@ -4831,16 +5243,16 @@
         <v>99</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="21">
         <v>5</v>
       </c>
@@ -4851,16 +5263,16 @@
         <v>97</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="21">
         <v>6</v>
       </c>
@@ -4871,16 +5283,16 @@
         <v>95</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="4">
         <v>7</v>
       </c>
@@ -4891,14 +5303,14 @@
         <v>93</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G11" s="12"/>
     </row>
-    <row r="12" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="21">
         <v>8</v>
       </c>
@@ -4909,16 +5321,16 @@
         <v>91</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="21">
         <v>9</v>
       </c>
@@ -4929,13 +5341,13 @@
         <v>89</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>
@@ -4947,7 +5359,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFC90DA2-F4E2-4199-984E-4595423FFE01}">
   <dimension ref="B2:G19"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="6" style="1" customWidth="1"/>
@@ -4959,26 +5371,26 @@
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:7" ht="21" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B3" s="16" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B4" s="5" t="s">
         <v>26</v>
       </c>
@@ -4989,16 +5401,16 @@
         <v>24</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="4">
         <v>1</v>
       </c>
@@ -5009,14 +5421,14 @@
         <v>86</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G5" s="12"/>
     </row>
-    <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="4">
         <v>2</v>
       </c>
@@ -5027,14 +5439,14 @@
         <v>113</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G6" s="12"/>
     </row>
-    <row r="7" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="11">
         <v>3</v>
       </c>
@@ -5045,16 +5457,16 @@
         <v>111</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="21">
         <v>4</v>
       </c>
@@ -5065,16 +5477,16 @@
         <v>110</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="11">
         <v>5</v>
       </c>
@@ -5085,16 +5497,16 @@
         <v>109</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="4">
         <v>6</v>
       </c>
@@ -5105,14 +5517,14 @@
         <v>108</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G10" s="12"/>
     </row>
-    <row r="11" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="4">
         <v>7</v>
       </c>
@@ -5123,14 +5535,14 @@
         <v>107</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G11" s="12"/>
     </row>
-    <row r="12" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="4">
         <v>8</v>
       </c>
@@ -5141,14 +5553,14 @@
         <v>106</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G12" s="12"/>
     </row>
-    <row r="13" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11">
         <v>9</v>
       </c>
@@ -5159,16 +5571,16 @@
         <v>65</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="11">
         <v>10</v>
       </c>
@@ -5179,16 +5591,16 @@
         <v>63</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="4">
         <v>11</v>
       </c>
@@ -5199,14 +5611,14 @@
         <v>105</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G15" s="12"/>
     </row>
-    <row r="16" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" s="4">
         <v>12</v>
       </c>
@@ -5217,14 +5629,14 @@
         <v>104</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G16" s="12"/>
     </row>
-    <row r="17" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="4">
         <v>13</v>
       </c>
@@ -5235,14 +5647,14 @@
         <v>57</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G17" s="12"/>
     </row>
-    <row r="18" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="21">
         <v>14</v>
       </c>
@@ -5253,16 +5665,16 @@
         <v>103</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="F18" s="18" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B19" s="21">
         <v>15</v>
       </c>
@@ -5273,13 +5685,13 @@
         <v>102</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F19" s="18" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G19" s="17" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
   </sheetData>
@@ -5291,7 +5703,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8B0CC9E-6722-48F3-8A9C-8DB6C697451D}">
   <dimension ref="B2:G10"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="6" style="1" customWidth="1"/>
@@ -5303,26 +5715,26 @@
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:7" ht="21" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B3" s="16" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B4" s="5" t="s">
         <v>26</v>
       </c>
@@ -5333,16 +5745,16 @@
         <v>24</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="11">
         <v>1</v>
       </c>
@@ -5353,16 +5765,16 @@
         <v>124</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="4">
         <v>2</v>
       </c>
@@ -5373,14 +5785,14 @@
         <v>86</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G6" s="12"/>
     </row>
-    <row r="7" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="4">
         <v>3</v>
       </c>
@@ -5391,14 +5803,14 @@
         <v>122</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G7" s="12"/>
     </row>
-    <row r="8" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="4">
         <v>4</v>
       </c>
@@ -5409,14 +5821,14 @@
         <v>120</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G8" s="12"/>
     </row>
-    <row r="9" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="4">
         <v>5</v>
       </c>
@@ -5427,14 +5839,14 @@
         <v>118</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="G9" s="12"/>
     </row>
-    <row r="10" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="4">
         <v>6</v>
       </c>
@@ -5445,10 +5857,10 @@
         <v>116</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G10" s="12"/>
     </row>
@@ -5461,7 +5873,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9314FFF7-DF8A-45E4-B313-537DCB7F9FA3}">
   <dimension ref="B2:G22"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="6" style="1" customWidth="1"/>
@@ -5473,26 +5885,26 @@
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:7" ht="21" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B3" s="16" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B4" s="5" t="s">
         <v>26</v>
       </c>
@@ -5503,16 +5915,16 @@
         <v>24</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="4">
         <v>1</v>
       </c>
@@ -5523,14 +5935,14 @@
         <v>86</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G5" s="12"/>
     </row>
-    <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="4">
         <v>2</v>
       </c>
@@ -5541,14 +5953,14 @@
         <v>137</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G6" s="12"/>
     </row>
-    <row r="7" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="11">
         <v>3</v>
       </c>
@@ -5559,16 +5971,16 @@
         <v>135</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="21">
         <v>4</v>
       </c>
@@ -5579,16 +5991,16 @@
         <v>133</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="4">
         <v>5</v>
       </c>
@@ -5599,14 +6011,14 @@
         <v>93</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G9" s="12"/>
     </row>
-    <row r="10" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="4">
         <v>6</v>
       </c>
@@ -5617,14 +6029,14 @@
         <v>131</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G10" s="12"/>
     </row>
-    <row r="11" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="4">
         <v>7</v>
       </c>
@@ -5635,14 +6047,14 @@
         <v>129</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G11" s="12"/>
     </row>
-    <row r="12" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="21">
         <v>8</v>
       </c>
@@ -5653,16 +6065,16 @@
         <v>128</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="11">
         <v>9</v>
       </c>
@@ -5673,16 +6085,16 @@
         <v>109</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="4">
         <v>10</v>
       </c>
@@ -5693,14 +6105,14 @@
         <v>127</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G14" s="12"/>
     </row>
-    <row r="15" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="4">
         <v>11</v>
       </c>
@@ -5711,14 +6123,14 @@
         <v>69</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G15" s="12"/>
     </row>
-    <row r="16" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" s="4">
         <v>12</v>
       </c>
@@ -5729,14 +6141,14 @@
         <v>67</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G16" s="12"/>
     </row>
-    <row r="17" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="11">
         <v>13</v>
       </c>
@@ -5747,16 +6159,16 @@
         <v>65</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="11">
         <v>14</v>
       </c>
@@ -5767,16 +6179,16 @@
         <v>63</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B19" s="4">
         <v>15</v>
       </c>
@@ -5787,14 +6199,14 @@
         <v>61</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G19" s="12"/>
     </row>
-    <row r="20" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B20" s="4">
         <v>16</v>
       </c>
@@ -5805,14 +6217,14 @@
         <v>104</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G20" s="12"/>
     </row>
-    <row r="21" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B21" s="4">
         <v>17</v>
       </c>
@@ -5823,14 +6235,14 @@
         <v>57</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G21" s="12"/>
     </row>
-    <row r="22" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="21">
         <v>18</v>
       </c>
@@ -5841,13 +6253,13 @@
         <v>103</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="F22" s="18" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -5859,7 +6271,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31CA4098-C87D-4F1E-9D32-152C4E925593}">
   <dimension ref="B2:G12"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="6" style="1" customWidth="1"/>
@@ -5871,26 +6283,26 @@
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:7" ht="21" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B3" s="16" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B4" s="5" t="s">
         <v>26</v>
       </c>
@@ -5901,16 +6313,16 @@
         <v>24</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="4">
         <v>1</v>
       </c>
@@ -5921,14 +6333,14 @@
         <v>86</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G5" s="12"/>
     </row>
-    <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="4">
         <v>2</v>
       </c>
@@ -5939,14 +6351,14 @@
         <v>152</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="G6" s="12"/>
     </row>
-    <row r="7" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="4">
         <v>3</v>
       </c>
@@ -5957,14 +6369,14 @@
         <v>150</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G7" s="12"/>
     </row>
-    <row r="8" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="4">
         <v>4</v>
       </c>
@@ -5975,14 +6387,14 @@
         <v>148</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G8" s="12"/>
     </row>
-    <row r="9" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="4">
         <v>5</v>
       </c>
@@ -5993,14 +6405,14 @@
         <v>146</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G9" s="12"/>
     </row>
-    <row r="10" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="4">
         <v>6</v>
       </c>
@@ -6011,14 +6423,14 @@
         <v>144</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G10" s="12"/>
     </row>
-    <row r="11" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="4">
         <v>7</v>
       </c>
@@ -6029,14 +6441,14 @@
         <v>142</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G11" s="12"/>
     </row>
-    <row r="12" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="4">
         <v>8</v>
       </c>
@@ -6047,10 +6459,10 @@
         <v>140</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G12" s="12"/>
     </row>
